--- a/EX1/Baseline_prediction_posteriors/EX1_baseline_effectiveness_all_models.xlsx
+++ b/EX1/Baseline_prediction_posteriors/EX1_baseline_effectiveness_all_models.xlsx
@@ -1,65 +1,82 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xhulj\Desktop\CPa\EX1\Baseline_prediction_posteriors\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84CF189C-B17C-499C-96FE-5C47999A7F9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="19940" yWindow="3340" windowWidth="17280" windowHeight="8880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="LApredict" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="DeepJIT" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="CodeBERT4JIT" sheetId="3" state="visible" r:id="rId4"/>
+    <sheet name="LApredict" sheetId="1" r:id="rId1"/>
+    <sheet name="DeepJIT" sheetId="2" r:id="rId2"/>
+    <sheet name="CodeBERT4JIT" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="31">
   <si>
-    <t xml:space="preserve">Correct predictions made by Lapredict</t>
+    <t>Correct predictions made by Lapredict</t>
   </si>
   <si>
-    <t xml:space="preserve">Predictions with prob. &gt; alpha</t>
+    <t>Predictions with prob. &gt; alpha</t>
   </si>
   <si>
     <t>Alpha</t>
   </si>
   <si>
-    <t xml:space="preserve">Data subset</t>
+    <t>Data subset</t>
   </si>
   <si>
-    <t xml:space="preserve">Total Rows</t>
+    <t>Total Rows</t>
   </si>
   <si>
-    <t xml:space="preserve">Tot. Correct Predictions</t>
+    <t>Tot. Correct Predictions</t>
   </si>
   <si>
-    <t xml:space="preserve">Tot. Correct Clean Predictions</t>
+    <t>Tot. Correct Clean Predictions</t>
   </si>
   <si>
-    <t xml:space="preserve">Tot. Correct Fault-prone Predictions</t>
+    <t>Tot. Correct Fault-prone Predictions</t>
   </si>
   <si>
-    <t xml:space="preserve">Nr. flagged predictions</t>
+    <t>Nr. flagged predictions</t>
   </si>
   <si>
-    <t xml:space="preserve">Nr. flagged Clean</t>
+    <t>Nr. flagged Clean</t>
   </si>
   <si>
-    <t xml:space="preserve">Nr. flagged Fault-prone</t>
+    <t>Nr. flagged Fault-prone</t>
   </si>
   <si>
-    <t xml:space="preserve">Nr. correctly flagged predictions</t>
+    <t>Nr. correctly flagged predictions</t>
   </si>
   <si>
-    <t xml:space="preserve">Nr. correctly flagged Clean</t>
+    <t>Nr. correctly flagged Clean</t>
   </si>
   <si>
-    <t xml:space="preserve">Nr. correctly flagged Fault-prone</t>
+    <t>Nr. correctly flagged Fault-prone</t>
   </si>
   <si>
     <t>Precision</t>
@@ -77,7 +94,7 @@
     <t>Recall-clean</t>
   </si>
   <si>
-    <t xml:space="preserve">Recall Fault-prone</t>
+    <t>Recall Fault-prone</t>
   </si>
   <si>
     <t xml:space="preserve">OPENSTACK </t>
@@ -89,16 +106,16 @@
     <t xml:space="preserve">AVG test </t>
   </si>
   <si>
-    <t xml:space="preserve">AVG Valid</t>
+    <t>AVG Valid</t>
   </si>
   <si>
     <t>0.9</t>
   </si>
   <si>
-    <t xml:space="preserve">Test AVG</t>
+    <t>Test AVG</t>
   </si>
   <si>
-    <t xml:space="preserve">Valid AVG</t>
+    <t>Valid AVG</t>
   </si>
   <si>
     <t>0.85</t>
@@ -107,107 +124,86 @@
     <t xml:space="preserve">QT </t>
   </si>
   <si>
-    <t xml:space="preserve">Test avg</t>
+    <t>Test avg</t>
   </si>
   <si>
-    <t xml:space="preserve">Valid avg</t>
-  </si>
-  <si>
-    <t>1197,276</t>
-  </si>
-  <si>
-    <t>704,9138</t>
-  </si>
-  <si>
-    <t>587,2241</t>
-  </si>
-  <si>
-    <t>117,6897</t>
-  </si>
-  <si>
-    <t>783,54</t>
-  </si>
-  <si>
-    <t>648,44</t>
-  </si>
-  <si>
-    <t>135,1</t>
+    <t>Valid avg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.000000"/>
-      <color theme="9" tint="0"/>
+      <sz val="11"/>
+      <color theme="9"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="11.000000"/>
-      <color theme="9" tint="0"/>
+      <sz val="11"/>
+      <color theme="9"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color theme="8" tint="0.39997558519241921"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color rgb="FF7030A0"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color theme="8" tint="-0.249977111117893"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color rgb="FF7030A0"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color theme="8" tint="-0.249977111117893"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color rgb="FF7030A0"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color theme="8" tint="-0.249977111117893"/>
       <name val="Calibri"/>
     </font>
@@ -222,35 +218,38 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="4">
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -265,7 +264,7 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -274,94 +273,104 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="0" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="43">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="1" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="2" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf fontId="2" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="8" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf fontId="3" fillId="3" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf fontId="2" fillId="3" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf fontId="2" fillId="4" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf fontId="2" fillId="4" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf fontId="2" fillId="0" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="4" fillId="0" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="1" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="1" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="6" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="5" fillId="3" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="7" fillId="3" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf fontId="8" fillId="4" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf fontId="8" fillId="4" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="6" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="5" fillId="0" borderId="0" numFmtId="1" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf fontId="6" fillId="0" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf fontId="5" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf fontId="6" fillId="0" borderId="0" numFmtId="165" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="165" xfId="0" applyNumberFormat="1"/>
-    <xf fontId="7" fillId="0" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf fontId="9" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="10" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="11" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="9" fillId="0" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -379,291 +388,8 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="1F497D"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="EEECE1"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4F81BD"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="C0504D"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="9BBB59"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8064A2"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4BACC6"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="F79646"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000FF"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="800080"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Angsana New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Cordia New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
-</file>
-
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -874,111 +600,113 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:R23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col customWidth="1" hidden="1" min="3" max="3" width="0"/>
-    <col customWidth="1" hidden="1" min="4" max="6" width="16"/>
-    <col customWidth="1" min="7" max="7" style="1" width="15.453125"/>
-    <col customWidth="1" min="8" max="9" width="7.875"/>
-    <col customWidth="1" min="10" max="10" style="1" width="15.90625"/>
-    <col customWidth="1" min="11" max="15" width="15.90625"/>
-    <col customWidth="1" min="16" max="16" width="12.453125"/>
+    <col min="3" max="3" width="0" hidden="1" customWidth="1"/>
+    <col min="4" max="6" width="16" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="15.44140625" style="1" customWidth="1"/>
+    <col min="8" max="9" width="7.88671875" customWidth="1"/>
+    <col min="10" max="10" width="15.88671875" style="1" customWidth="1"/>
+    <col min="11" max="15" width="15.88671875" customWidth="1"/>
+    <col min="16" max="16" width="12.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="D1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="3" t="s">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="D1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-    </row>
-    <row r="2" ht="28" customHeight="1">
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+    </row>
+    <row r="2" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="J2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="L2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="10" t="s">
+      <c r="M2" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="N2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="O2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="P2" s="11" t="s">
+      <c r="P2" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="Q2" s="12" t="s">
+      <c r="Q2" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="R2" s="12" t="s">
+      <c r="R2" s="9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="13" t="s">
+    <row r="4" spans="1:18" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="14"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13"/>
-      <c r="M4" s="13"/>
-      <c r="N4" s="13"/>
-      <c r="O4" s="13"/>
-      <c r="P4" s="13"/>
-    </row>
-    <row r="5">
+      <c r="B4" s="32"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="33"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="32"/>
+      <c r="J4" s="33"/>
+      <c r="K4" s="32"/>
+      <c r="L4" s="32"/>
+      <c r="M4" s="32"/>
+      <c r="N4" s="32"/>
+      <c r="O4" s="32"/>
+      <c r="P4" s="32"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -1015,7 +743,7 @@
       <c r="L5">
         <v>9</v>
       </c>
-      <c r="M5" s="15">
+      <c r="M5" s="10">
         <v>0.94594594594594583</v>
       </c>
       <c r="N5">
@@ -1024,54 +752,54 @@
       <c r="O5">
         <v>0.81818181818181823</v>
       </c>
-      <c r="P5" s="15">
-        <v>0.04720798489344484</v>
-      </c>
-      <c r="Q5" s="16">
-        <v>0.047347404449515122</v>
-      </c>
-      <c r="R5" s="16">
-        <v>0.044776119402985079</v>
-      </c>
-    </row>
-    <row r="6">
+      <c r="P5" s="10">
+        <v>4.720798489344484E-2</v>
+      </c>
+      <c r="Q5" s="11">
+        <v>4.7347404449515122E-2</v>
+      </c>
+      <c r="R5" s="11">
+        <v>4.4776119402985079E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>21</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="12">
         <v>1820.5172413793102</v>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="12">
         <v>1359.3218390804598</v>
       </c>
-      <c r="E6" s="17">
+      <c r="E6" s="12">
         <v>1260.3563218390805</v>
       </c>
-      <c r="F6" s="17">
+      <c r="F6" s="12">
         <v>98.965517241379317</v>
       </c>
-      <c r="G6" s="18">
+      <c r="G6" s="13">
         <v>104.33333333333333</v>
       </c>
-      <c r="H6" s="17">
+      <c r="H6" s="12">
         <v>101.49425287356321</v>
       </c>
-      <c r="I6" s="17">
+      <c r="I6" s="12">
         <v>2.8390804597701149</v>
       </c>
-      <c r="J6" s="18">
+      <c r="J6" s="13">
         <v>99.724137931034477</v>
       </c>
-      <c r="K6" s="17">
+      <c r="K6" s="12">
         <v>98.275862068965523</v>
       </c>
-      <c r="L6" s="17">
+      <c r="L6" s="12">
         <v>1.4482758620689655</v>
       </c>
-      <c r="M6" s="15">
+      <c r="M6" s="10">
         <v>0.95589590919754097</v>
       </c>
       <c r="N6">
@@ -1080,21 +808,21 @@
       <c r="O6">
         <v>0.53497536945812807</v>
       </c>
-      <c r="P6" s="15">
-        <v>0.073359030914489115</v>
+      <c r="P6" s="10">
+        <v>7.3359030914489115E-2</v>
       </c>
       <c r="Q6">
-        <v>0.077957299123665752</v>
+        <v>7.7957299123665752E-2</v>
       </c>
       <c r="R6">
-        <v>0.01458962348005291</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="M7" s="15"/>
-      <c r="P7" s="15"/>
-    </row>
-    <row r="8">
+        <v>1.458962348005291E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="M7" s="10"/>
+      <c r="P7" s="10"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -1131,7 +859,7 @@
       <c r="L8">
         <v>12</v>
       </c>
-      <c r="M8" s="15">
+      <c r="M8" s="10">
         <v>0.92405063291139222</v>
       </c>
       <c r="N8">
@@ -1140,17 +868,17 @@
       <c r="O8">
         <v>0.75</v>
       </c>
-      <c r="P8" s="15">
+      <c r="P8" s="10">
         <v>0.11815484219045048</v>
       </c>
-      <c r="Q8" s="16">
+      <c r="Q8" s="11">
         <v>0.1215059897318882</v>
       </c>
-      <c r="R8" s="16">
-        <v>0.059701492537313432</v>
-      </c>
-    </row>
-    <row r="9">
+      <c r="R8" s="11">
+        <v>5.9701492537313432E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -1169,7 +897,7 @@
       <c r="F9">
         <v>98.965517241379317</v>
       </c>
-      <c r="G9" s="18">
+      <c r="G9" s="13">
         <v>205.18390804597701</v>
       </c>
       <c r="H9">
@@ -1187,7 +915,7 @@
       <c r="L9">
         <v>4.1034482758620694</v>
       </c>
-      <c r="M9" s="15">
+      <c r="M9" s="10">
         <v>0.93024130642327951</v>
       </c>
       <c r="N9">
@@ -1196,21 +924,21 @@
       <c r="O9">
         <v>0.66989606817193026</v>
       </c>
-      <c r="P9" s="15">
+      <c r="P9" s="10">
         <v>0.14041214291895668</v>
       </c>
       <c r="Q9">
         <v>0.14816037180233008</v>
       </c>
       <c r="R9">
-        <v>0.041299047689924567</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="M10" s="15"/>
-      <c r="P10" s="15"/>
-    </row>
-    <row r="11">
+        <v>4.1299047689924567E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="M10" s="10"/>
+      <c r="P10" s="10"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -1247,7 +975,7 @@
       <c r="L11">
         <v>20</v>
       </c>
-      <c r="M11" s="15">
+      <c r="M11" s="10">
         <v>0.93081081081081074</v>
       </c>
       <c r="N11">
@@ -1256,17 +984,17 @@
       <c r="O11">
         <v>0.79999999999999993</v>
       </c>
-      <c r="P11" s="15">
+      <c r="P11" s="10">
         <v>0.23226328567574855</v>
       </c>
-      <c r="Q11" s="16">
+      <c r="Q11" s="11">
         <v>0.23987450085567599</v>
       </c>
-      <c r="R11" s="16">
-        <v>0.09950248756218906</v>
-      </c>
-    </row>
-    <row r="12">
+      <c r="R11" s="11">
+        <v>9.950248756218906E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -1285,7 +1013,7 @@
       <c r="F12">
         <v>98.965517241379317</v>
       </c>
-      <c r="G12" s="18">
+      <c r="G12" s="13">
         <v>361.89655172413791</v>
       </c>
       <c r="H12">
@@ -1303,7 +1031,7 @@
       <c r="L12">
         <v>6.8850574712643677</v>
       </c>
-      <c r="M12" s="15">
+      <c r="M12" s="10">
         <v>0.90447429234530075</v>
       </c>
       <c r="N12">
@@ -1312,37 +1040,37 @@
       <c r="O12">
         <v>0.69682391783117736</v>
       </c>
-      <c r="P12" s="15">
+      <c r="P12" s="10">
         <v>0.24080536671930963</v>
       </c>
       <c r="Q12">
         <v>0.25422548142218399</v>
       </c>
       <c r="R12">
-        <v>0.069528877831974464</v>
-      </c>
-    </row>
-    <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="13" t="s">
+        <v>6.9528877831974464E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="14"/>
-      <c r="K15" s="13"/>
-      <c r="L15" s="13"/>
-      <c r="M15" s="13"/>
-      <c r="N15" s="13"/>
-      <c r="O15" s="13"/>
-      <c r="P15" s="13"/>
-    </row>
-    <row r="16">
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="33"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="33"/>
+      <c r="K15" s="32"/>
+      <c r="L15" s="32"/>
+      <c r="M15" s="32"/>
+      <c r="N15" s="32"/>
+      <c r="O15" s="32"/>
+      <c r="P15" s="32"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -1356,10 +1084,10 @@
         <v>4052</v>
       </c>
       <c r="E16">
-        <v>4003.5999999999999</v>
+        <v>4003.6</v>
       </c>
       <c r="F16">
-        <v>48.399999999999999</v>
+        <v>48.4</v>
       </c>
       <c r="G16" s="1">
         <v>51</v>
@@ -1379,7 +1107,7 @@
       <c r="L16">
         <v>0</v>
       </c>
-      <c r="M16" s="15">
+      <c r="M16" s="10">
         <v>0.90196078431372562</v>
       </c>
       <c r="N16">
@@ -1388,17 +1116,17 @@
       <c r="O16">
         <v>0</v>
       </c>
-      <c r="P16" s="15">
-        <v>0.011352517345668032</v>
-      </c>
-      <c r="Q16" s="16">
-        <v>0.011489936674755636</v>
+      <c r="P16" s="10">
+        <v>1.1352517345668032E-2</v>
+      </c>
+      <c r="Q16" s="11">
+        <v>1.1489936674755636E-2</v>
       </c>
       <c r="R16">
         <v>0</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -1406,36 +1134,36 @@
         <v>30</v>
       </c>
       <c r="C17">
-        <v>1912.9000000000001</v>
+        <v>1912.9</v>
       </c>
       <c r="D17">
         <v>1616.5</v>
       </c>
       <c r="E17">
-        <v>1589.3399999999999</v>
+        <v>1589.34</v>
       </c>
       <c r="F17">
         <v>27.16</v>
       </c>
       <c r="G17" s="1">
-        <v>31.039999999999999</v>
+        <v>31.04</v>
       </c>
       <c r="H17">
-        <v>30.550000000000001</v>
+        <v>30.55</v>
       </c>
       <c r="I17">
-        <v>0.48999999999999999</v>
+        <v>0.49</v>
       </c>
       <c r="J17" s="1">
-        <v>28.890000000000001</v>
+        <v>28.89</v>
       </c>
       <c r="K17">
-        <v>28.629999999999999</v>
+        <v>28.63</v>
       </c>
       <c r="L17">
-        <v>0.26000000000000001</v>
-      </c>
-      <c r="M17" s="15">
+        <v>0.26</v>
+      </c>
+      <c r="M17" s="10">
         <v>0.93201322179392621</v>
       </c>
       <c r="N17">
@@ -1444,21 +1172,21 @@
       <c r="O17">
         <v>0.23499999999999999</v>
       </c>
-      <c r="P17" s="15">
-        <v>0.017874938991986077</v>
+      <c r="P17" s="10">
+        <v>1.7874938991986077E-2</v>
       </c>
       <c r="Q17">
-        <v>0.018017936690040214</v>
+        <v>1.8017936690040214E-2</v>
       </c>
       <c r="R17">
-        <v>0.010587552771074794</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="M18" s="15"/>
-      <c r="P18" s="15"/>
-    </row>
-    <row r="19">
+        <v>1.0587552771074794E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="M18" s="10"/>
+      <c r="P18" s="10"/>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -1472,10 +1200,10 @@
         <v>4052</v>
       </c>
       <c r="E19">
-        <v>4003.5999999999999</v>
+        <v>4003.6</v>
       </c>
       <c r="F19">
-        <v>48.399999999999999</v>
+        <v>48.4</v>
       </c>
       <c r="G19" s="1">
         <v>1687</v>
@@ -1495,7 +1223,7 @@
       <c r="L19">
         <v>0</v>
       </c>
-      <c r="M19" s="15">
+      <c r="M19" s="10">
         <v>0.92531120331950212</v>
       </c>
       <c r="N19">
@@ -1504,17 +1232,17 @@
       <c r="O19">
         <v>0</v>
       </c>
-      <c r="P19" s="15">
+      <c r="P19" s="10">
         <v>0.38524520818669117</v>
       </c>
-      <c r="Q19" s="16">
+      <c r="Q19" s="11">
         <v>0.38990850324551196</v>
       </c>
       <c r="R19">
         <v>0</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -1522,36 +1250,36 @@
         <v>30</v>
       </c>
       <c r="C20">
-        <v>1912.9000000000001</v>
+        <v>1912.9</v>
       </c>
       <c r="D20">
         <v>1616.5</v>
       </c>
       <c r="E20">
-        <v>1589.3399999999999</v>
+        <v>1589.34</v>
       </c>
       <c r="F20">
         <v>27.16</v>
       </c>
       <c r="G20" s="1">
-        <v>692.20000000000005</v>
+        <v>692.2</v>
       </c>
       <c r="H20">
         <v>691.13</v>
       </c>
       <c r="I20">
-        <v>1.0700000000000001</v>
+        <v>1.07</v>
       </c>
       <c r="J20" s="1">
-        <v>641.09000000000003</v>
+        <v>641.09</v>
       </c>
       <c r="K20">
         <v>640.45000000000005</v>
       </c>
       <c r="L20">
-        <v>0.64000000000000001</v>
-      </c>
-      <c r="M20" s="15">
+        <v>0.64</v>
+      </c>
+      <c r="M20" s="10">
         <v>0.92637758387128288</v>
       </c>
       <c r="N20">
@@ -1560,21 +1288,21 @@
       <c r="O20">
         <v>0.38850000000000001</v>
       </c>
-      <c r="P20" s="15">
+      <c r="P20" s="10">
         <v>0.39666086047024651</v>
       </c>
       <c r="Q20">
         <v>0.40304906004926666</v>
       </c>
       <c r="R20">
-        <v>0.025936622902027605</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="M21" s="15"/>
-      <c r="P21" s="15"/>
-    </row>
-    <row r="22">
+        <v>2.5936622902027605E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="M21" s="10"/>
+      <c r="P21" s="10"/>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>27</v>
       </c>
@@ -1588,10 +1316,10 @@
         <v>4052</v>
       </c>
       <c r="E22">
-        <v>4003.5999999999999</v>
+        <v>4003.6</v>
       </c>
       <c r="F22">
-        <v>48.399999999999999</v>
+        <v>48.4</v>
       </c>
       <c r="G22" s="1">
         <v>3089</v>
@@ -1611,7 +1339,7 @@
       <c r="L22">
         <v>1</v>
       </c>
-      <c r="M22" s="15">
+      <c r="M22" s="10">
         <v>0.9015862738750402</v>
       </c>
       <c r="N22">
@@ -1620,17 +1348,17 @@
       <c r="O22">
         <v>0.25</v>
       </c>
-      <c r="P22" s="15">
+      <c r="P22" s="10">
         <v>0.68732088712359718</v>
       </c>
-      <c r="Q22" s="16">
+      <c r="Q22" s="11">
         <v>0.6953909500547758</v>
       </c>
-      <c r="R22" s="16">
-        <v>0.021647058823529408</v>
-      </c>
-    </row>
-    <row r="23">
+      <c r="R22" s="11">
+        <v>2.1647058823529408E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>27</v>
       </c>
@@ -1638,13 +1366,13 @@
         <v>30</v>
       </c>
       <c r="C23">
-        <v>1912.9000000000001</v>
+        <v>1912.9</v>
       </c>
       <c r="D23">
         <v>1616.5</v>
       </c>
       <c r="E23">
-        <v>1589.3399999999999</v>
+        <v>1589.34</v>
       </c>
       <c r="F23">
         <v>27.16</v>
@@ -1665,9 +1393,9 @@
         <v>1127.3399999999999</v>
       </c>
       <c r="L23">
-        <v>0.89000000000000001</v>
-      </c>
-      <c r="M23" s="15">
+        <v>0.89</v>
+      </c>
+      <c r="M23" s="10">
         <v>0.90489731188596967</v>
       </c>
       <c r="N23">
@@ -1676,14 +1404,14 @@
       <c r="O23">
         <v>0.40016666666666673</v>
       </c>
-      <c r="P23" s="15">
+      <c r="P23" s="10">
         <v>0.69798167731187843</v>
       </c>
       <c r="Q23">
         <v>0.70936400714902093</v>
       </c>
       <c r="R23">
-        <v>0.035518231244896302</v>
+        <v>3.5518231244896302E-2</v>
       </c>
     </row>
   </sheetData>
@@ -1693,137 +1421,136 @@
     <mergeCell ref="A4:P4"/>
     <mergeCell ref="A15:P15"/>
   </mergeCells>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:R23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col customWidth="1" min="3" max="5" width="10.36328125"/>
-    <col customWidth="1" min="6" max="6" width="9.36328125"/>
-    <col customWidth="1" min="7" max="7" style="19" width="19.375"/>
-    <col customWidth="1" min="8" max="9" width="6.125"/>
-    <col customWidth="1" min="10" max="10" style="1" width="12.375"/>
-    <col customWidth="1" min="11" max="12" width="8.81640625"/>
-    <col bestFit="1" customWidth="1" min="13" max="13" style="20" width="8.81640625"/>
-    <col customWidth="1" min="14" max="15" width="8.81640625"/>
-    <col bestFit="1" customWidth="1" min="16" max="16" style="20" width="8.81640625"/>
-    <col bestFit="1" customWidth="1" min="17" max="18" width="8.81640625"/>
+    <col min="3" max="5" width="10.33203125" customWidth="1"/>
+    <col min="6" max="6" width="9.33203125" customWidth="1"/>
+    <col min="7" max="7" width="19.33203125" style="14" customWidth="1"/>
+    <col min="8" max="9" width="6.109375" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" style="1" customWidth="1"/>
+    <col min="11" max="12" width="8.77734375" customWidth="1"/>
+    <col min="13" max="13" width="8.77734375" style="15" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="8.77734375" customWidth="1"/>
+    <col min="16" max="16" width="8.77734375" style="15" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="8.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="D1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="21" t="s">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="D1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-    </row>
-    <row r="2" ht="28" customHeight="1">
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+    </row>
+    <row r="2" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="22" t="s">
+      <c r="G2" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="J2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="L2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="23" t="s">
+      <c r="M2" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="N2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="O2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="P2" s="24" t="s">
+      <c r="P2" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="Q2" s="12" t="s">
+      <c r="Q2" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="R2" s="12" t="s">
+      <c r="R2" s="9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="13" t="s">
+    <row r="4" spans="1:18" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="14"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13"/>
-      <c r="M4" s="26"/>
-      <c r="N4" s="13"/>
-      <c r="O4" s="13"/>
-      <c r="P4" s="26"/>
-    </row>
-    <row r="5">
+      <c r="B4" s="32"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="32"/>
+      <c r="J4" s="33"/>
+      <c r="K4" s="32"/>
+      <c r="L4" s="32"/>
+      <c r="M4" s="36"/>
+      <c r="N4" s="32"/>
+      <c r="O4" s="32"/>
+      <c r="P4" s="36"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>21</v>
       </c>
       <c r="B5" t="s">
         <v>29</v>
       </c>
-      <c r="C5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="F5" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="G5" s="19">
+      <c r="C5">
+        <v>1331</v>
+      </c>
+      <c r="D5" s="12">
+        <v>793.3</v>
+      </c>
+      <c r="E5" s="12">
+        <v>659.3</v>
+      </c>
+      <c r="F5" s="12">
+        <v>134</v>
+      </c>
+      <c r="G5" s="14">
         <v>0</v>
       </c>
       <c r="H5">
@@ -1841,7 +1568,7 @@
       <c r="L5">
         <v>0</v>
       </c>
-      <c r="M5" s="20">
+      <c r="M5" s="15">
         <v>0</v>
       </c>
       <c r="N5">
@@ -1850,7 +1577,7 @@
       <c r="O5">
         <v>0</v>
       </c>
-      <c r="P5" s="20">
+      <c r="P5" s="15">
         <v>0</v>
       </c>
       <c r="Q5">
@@ -1860,26 +1587,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>21</v>
       </c>
       <c r="B6" t="s">
         <v>30</v>
       </c>
-      <c r="C6">
-        <v>1331</v>
-      </c>
-      <c r="D6" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G6" s="19">
+      <c r="C6" s="12">
+        <v>1197.5999999999999</v>
+      </c>
+      <c r="D6" s="12">
+        <v>736.41</v>
+      </c>
+      <c r="E6" s="12">
+        <v>611.15</v>
+      </c>
+      <c r="F6" s="12">
+        <v>125.26</v>
+      </c>
+      <c r="G6" s="14">
         <v>0</v>
       </c>
       <c r="H6">
@@ -1897,7 +1624,7 @@
       <c r="L6">
         <v>0</v>
       </c>
-      <c r="M6" s="20">
+      <c r="M6" s="15">
         <v>0</v>
       </c>
       <c r="N6">
@@ -1906,7 +1633,7 @@
       <c r="O6">
         <v>0</v>
       </c>
-      <c r="P6" s="20">
+      <c r="P6" s="15">
         <v>0</v>
       </c>
       <c r="Q6">
@@ -1916,7 +1643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -1926,16 +1653,16 @@
       <c r="C8">
         <v>1331</v>
       </c>
-      <c r="D8" s="17">
-        <v>784.89999999999998</v>
-      </c>
-      <c r="E8" s="17">
-        <v>650.04999999999995</v>
-      </c>
-      <c r="F8" s="17">
-        <v>134.84999999999999</v>
-      </c>
-      <c r="G8" s="19">
+      <c r="D8" s="12">
+        <v>794</v>
+      </c>
+      <c r="E8" s="12">
+        <v>660</v>
+      </c>
+      <c r="F8" s="12">
+        <v>134</v>
+      </c>
+      <c r="G8" s="14">
         <v>0</v>
       </c>
       <c r="H8">
@@ -1953,7 +1680,7 @@
       <c r="L8">
         <v>0</v>
       </c>
-      <c r="M8" s="20">
+      <c r="M8" s="15">
         <v>0</v>
       </c>
       <c r="N8">
@@ -1962,7 +1689,7 @@
       <c r="O8">
         <v>0</v>
       </c>
-      <c r="P8" s="20">
+      <c r="P8" s="15">
         <v>0</v>
       </c>
       <c r="Q8">
@@ -1972,26 +1699,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>24</v>
       </c>
       <c r="B9" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="12">
         <v>1197.5999999999999</v>
       </c>
-      <c r="D9" s="17">
-        <v>712.79999999999995</v>
-      </c>
-      <c r="E9" s="17">
-        <v>594.79999999999995</v>
-      </c>
-      <c r="F9" s="17">
-        <v>118</v>
-      </c>
-      <c r="G9" s="19">
+      <c r="D9" s="12">
+        <v>737</v>
+      </c>
+      <c r="E9" s="12">
+        <v>612</v>
+      </c>
+      <c r="F9" s="12">
+        <v>125</v>
+      </c>
+      <c r="G9" s="14">
         <v>0</v>
       </c>
       <c r="H9">
@@ -2009,7 +1736,7 @@
       <c r="L9">
         <v>0</v>
       </c>
-      <c r="M9" s="20">
+      <c r="M9" s="15">
         <v>0</v>
       </c>
       <c r="N9">
@@ -2018,7 +1745,7 @@
       <c r="O9">
         <v>0</v>
       </c>
-      <c r="P9" s="20">
+      <c r="P9" s="15">
         <v>0</v>
       </c>
       <c r="Q9">
@@ -2028,7 +1755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -2038,465 +1765,465 @@
       <c r="C11">
         <v>1331</v>
       </c>
-      <c r="D11" s="17">
-        <v>775</v>
-      </c>
-      <c r="E11" s="17">
-        <v>638.46000000000004</v>
-      </c>
-      <c r="F11" s="17">
-        <v>136.53999999999999</v>
-      </c>
-      <c r="G11" s="27">
-        <v>41.960000000000001</v>
-      </c>
-      <c r="H11" s="17">
-        <v>25.059999999999999</v>
-      </c>
-      <c r="I11" s="17">
-        <v>16.899999999999999</v>
-      </c>
-      <c r="J11" s="18">
-        <v>28.579999999999998</v>
-      </c>
-      <c r="K11" s="17">
-        <v>24.739999999999998</v>
-      </c>
-      <c r="L11" s="17">
-        <v>3.8399999999999999</v>
-      </c>
-      <c r="M11" s="28">
-        <v>0.67043251037016571</v>
-      </c>
-      <c r="N11" s="16">
-        <v>0.99016300091925913</v>
-      </c>
-      <c r="O11" s="16">
-        <v>0.23851846680522509</v>
-      </c>
-      <c r="P11" s="28">
-        <v>0.036585264725460871</v>
-      </c>
-      <c r="Q11" s="16">
-        <v>0.038100215663805198</v>
-      </c>
-      <c r="R11" s="16">
-        <v>0.02767788819221929</v>
-      </c>
-    </row>
-    <row r="12">
+      <c r="D11" s="12">
+        <v>763.5</v>
+      </c>
+      <c r="E11" s="12">
+        <v>628.20000000000005</v>
+      </c>
+      <c r="F11" s="12">
+        <v>135.30000000000001</v>
+      </c>
+      <c r="G11" s="19">
+        <v>42.4</v>
+      </c>
+      <c r="H11" s="12">
+        <v>26</v>
+      </c>
+      <c r="I11" s="12">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="J11" s="13">
+        <v>29.4</v>
+      </c>
+      <c r="K11" s="12">
+        <v>25.7</v>
+      </c>
+      <c r="L11" s="12">
+        <v>3.7</v>
+      </c>
+      <c r="M11" s="20">
+        <v>0.67219648110612795</v>
+      </c>
+      <c r="N11" s="11">
+        <v>0.99192400189629626</v>
+      </c>
+      <c r="O11" s="11">
+        <v>0.25876068380073264</v>
+      </c>
+      <c r="P11" s="20">
+        <v>3.7777172854017799E-2</v>
+      </c>
+      <c r="Q11" s="11">
+        <v>3.9524430257438035E-2</v>
+      </c>
+      <c r="R11" s="11">
+        <v>2.6845000949617025E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>27</v>
       </c>
       <c r="B12" t="s">
         <v>30</v>
       </c>
-      <c r="C12">
-        <v>1197.3793103448277</v>
-      </c>
-      <c r="D12" s="17">
-        <v>695.5344827586207</v>
-      </c>
-      <c r="E12" s="17">
-        <v>576.62068965517244</v>
-      </c>
-      <c r="F12" s="17">
-        <v>118.91379310344827</v>
-      </c>
-      <c r="G12" s="27">
-        <v>35.551724137931032</v>
-      </c>
-      <c r="H12" s="17">
-        <v>21.637931034482758</v>
-      </c>
-      <c r="I12" s="17">
-        <v>13.913793103448276</v>
-      </c>
-      <c r="J12" s="18">
-        <v>27</v>
-      </c>
-      <c r="K12" s="17">
-        <v>21.327586206896552</v>
-      </c>
-      <c r="L12" s="17">
-        <v>5.6724137931034484</v>
-      </c>
-      <c r="M12" s="28">
-        <v>0.73775150143782953</v>
-      </c>
-      <c r="N12" s="16">
-        <v>0.98047127986206895</v>
-      </c>
-      <c r="O12" s="16">
-        <v>0.39608932641644568</v>
-      </c>
-      <c r="P12" s="28">
-        <v>0.038547275608692269</v>
-      </c>
-      <c r="Q12" s="16">
-        <v>0.036332606567887865</v>
-      </c>
-      <c r="R12" s="16">
-        <v>0.046871153084499677</v>
-      </c>
-    </row>
-    <row r="13" ht="14.25">
-      <c r="M13" s="28"/>
-    </row>
-    <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="13" t="s">
+      <c r="C12" s="12">
+        <v>1197.5999999999999</v>
+      </c>
+      <c r="D12" s="12">
+        <v>702.38</v>
+      </c>
+      <c r="E12" s="12">
+        <v>578.91999999999996</v>
+      </c>
+      <c r="F12" s="12">
+        <v>123.46</v>
+      </c>
+      <c r="G12" s="19">
+        <v>37.14</v>
+      </c>
+      <c r="H12" s="12">
+        <v>21.37</v>
+      </c>
+      <c r="I12" s="12">
+        <v>15.77</v>
+      </c>
+      <c r="J12" s="13">
+        <v>26.5</v>
+      </c>
+      <c r="K12" s="12">
+        <v>21.06</v>
+      </c>
+      <c r="L12" s="12">
+        <v>5.44</v>
+      </c>
+      <c r="M12" s="20">
+        <v>0.69642153264518514</v>
+      </c>
+      <c r="N12" s="11">
+        <v>0.9820744629999999</v>
+      </c>
+      <c r="O12" s="11">
+        <v>0.3564962448894623</v>
+      </c>
+      <c r="P12" s="20">
+        <v>3.7415104240963656E-2</v>
+      </c>
+      <c r="Q12" s="11">
+        <v>3.5633398871168828E-2</v>
+      </c>
+      <c r="R12" s="11">
+        <v>4.3600505590592552E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="M13" s="20"/>
+    </row>
+    <row r="15" spans="1:18" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="14"/>
-      <c r="K15" s="13"/>
-      <c r="L15" s="13"/>
-      <c r="M15" s="26"/>
-      <c r="N15" s="13"/>
-      <c r="O15" s="13"/>
-      <c r="P15" s="26"/>
-    </row>
-    <row r="16">
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="35"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="33"/>
+      <c r="K15" s="32"/>
+      <c r="L15" s="32"/>
+      <c r="M15" s="36"/>
+      <c r="N15" s="32"/>
+      <c r="O15" s="32"/>
+      <c r="P15" s="36"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>21</v>
       </c>
       <c r="B16" t="s">
         <v>25</v>
       </c>
-      <c r="C16" s="17">
+      <c r="C16" s="12">
         <v>2571</v>
       </c>
-      <c r="D16" s="17">
-        <v>1843.0599999999999</v>
-      </c>
-      <c r="E16" s="17">
-        <v>1720.3800000000001</v>
-      </c>
-      <c r="F16" s="17">
-        <v>122.68000000000001</v>
-      </c>
-      <c r="G16" s="29">
-        <v>0.80000000000000004</v>
-      </c>
-      <c r="H16" s="30">
-        <v>0.10000000000000001</v>
-      </c>
-      <c r="I16" s="30">
-        <v>0.69999999999999996</v>
-      </c>
-      <c r="J16" s="31">
-        <v>0.41999999999999998</v>
-      </c>
-      <c r="K16" s="30">
-        <v>0.10000000000000001</v>
-      </c>
-      <c r="L16" s="30">
-        <v>0.32000000000000001</v>
-      </c>
-      <c r="M16" s="32">
-        <v>0.14866666666</v>
-      </c>
-      <c r="N16" s="33">
-        <v>0.040000000000000001</v>
-      </c>
-      <c r="O16" s="33">
-        <v>0.12666666666000001</v>
-      </c>
-      <c r="P16" s="32">
-        <v>0.00022934842000000004</v>
-      </c>
-      <c r="Q16" s="33">
-        <v>5.8200480000000005e-05</v>
-      </c>
-      <c r="R16" s="33">
-        <v>0.0025924146200000005</v>
-      </c>
-    </row>
-    <row r="17">
+      <c r="D16" s="12">
+        <v>1847.6</v>
+      </c>
+      <c r="E16" s="12">
+        <v>1725.5</v>
+      </c>
+      <c r="F16" s="12">
+        <v>122.1</v>
+      </c>
+      <c r="G16" s="21">
+        <v>0.7</v>
+      </c>
+      <c r="H16" s="22">
+        <v>0</v>
+      </c>
+      <c r="I16" s="22">
+        <v>0.7</v>
+      </c>
+      <c r="J16" s="23">
+        <v>0.3</v>
+      </c>
+      <c r="K16" s="22">
+        <v>0</v>
+      </c>
+      <c r="L16" s="22">
+        <v>0.3</v>
+      </c>
+      <c r="M16" s="24">
+        <v>0.2</v>
+      </c>
+      <c r="N16" s="25">
+        <v>0</v>
+      </c>
+      <c r="O16" s="25">
+        <v>0.2</v>
+      </c>
+      <c r="P16" s="24">
+        <v>1.5938580000000001E-4</v>
+      </c>
+      <c r="Q16" s="25">
+        <v>0</v>
+      </c>
+      <c r="R16" s="25">
+        <v>2.486912E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>21</v>
       </c>
       <c r="B17" t="s">
         <v>26</v>
       </c>
-      <c r="C17" s="17">
+      <c r="C17" s="12">
         <v>2280.0149253731342</v>
       </c>
-      <c r="D17" s="17">
-        <v>1659.0298507462687</v>
-      </c>
-      <c r="E17" s="17">
-        <v>1539.2835820895523</v>
-      </c>
-      <c r="F17" s="17">
-        <v>119.74626865671642</v>
-      </c>
-      <c r="G17" s="29">
-        <v>1.4029850746268657</v>
-      </c>
-      <c r="H17" s="30">
-        <v>0.35820895522388058</v>
-      </c>
-      <c r="I17" s="30">
-        <v>1.044776119402985</v>
-      </c>
-      <c r="J17" s="31">
-        <v>0.92537313432835822</v>
-      </c>
-      <c r="K17" s="30">
-        <v>0.35820895522388058</v>
-      </c>
-      <c r="L17" s="30">
-        <v>0.56716417910447758</v>
-      </c>
-      <c r="M17" s="32">
-        <v>0.25087881058208955</v>
-      </c>
-      <c r="N17" s="33">
-        <v>0.059701492537313432</v>
-      </c>
-      <c r="O17" s="33">
-        <v>0.21561833688059701</v>
-      </c>
-      <c r="P17" s="32">
-        <v>0.0010468290047372434</v>
-      </c>
-      <c r="Q17" s="33">
-        <v>0.00059385494029850746</v>
-      </c>
-      <c r="R17" s="33">
-        <v>0.0047320709634379697</v>
-      </c>
-    </row>
-    <row r="19">
+      <c r="D17" s="12">
+        <v>1683.31</v>
+      </c>
+      <c r="E17" s="12">
+        <v>1565.06</v>
+      </c>
+      <c r="F17" s="12">
+        <v>120.25</v>
+      </c>
+      <c r="G17" s="21">
+        <v>0.54</v>
+      </c>
+      <c r="H17" s="22">
+        <v>0.06</v>
+      </c>
+      <c r="I17" s="22">
+        <v>0.48</v>
+      </c>
+      <c r="J17" s="23">
+        <v>0.37</v>
+      </c>
+      <c r="K17" s="22">
+        <v>0.06</v>
+      </c>
+      <c r="L17" s="22">
+        <v>0.31</v>
+      </c>
+      <c r="M17" s="24">
+        <v>0.23666666667000003</v>
+      </c>
+      <c r="N17" s="25">
+        <v>0.03</v>
+      </c>
+      <c r="O17" s="25">
+        <v>0.20666666667</v>
+      </c>
+      <c r="P17" s="24">
+        <v>2.189483363479058E-4</v>
+      </c>
+      <c r="Q17" s="25">
+        <v>3.7499999999999997E-5</v>
+      </c>
+      <c r="R17" s="25">
+        <v>2.6219458210068793E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>24</v>
       </c>
       <c r="B19" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="17">
+      <c r="C19" s="12">
         <v>2571</v>
       </c>
-      <c r="D19" s="17">
-        <v>1843.0599999999999</v>
-      </c>
-      <c r="E19" s="17">
-        <v>1720.3800000000001</v>
-      </c>
-      <c r="F19" s="17">
-        <v>122.68000000000001</v>
-      </c>
-      <c r="G19" s="27">
-        <v>93.900000000000006</v>
-      </c>
-      <c r="H19" s="17">
-        <v>42.380000000000003</v>
-      </c>
-      <c r="I19" s="17">
-        <v>51.520000000000003</v>
-      </c>
-      <c r="J19" s="18">
-        <v>58.340000000000003</v>
-      </c>
-      <c r="K19" s="17">
-        <v>42.380000000000003</v>
-      </c>
-      <c r="L19" s="17">
-        <v>15.960000000000001</v>
-      </c>
-      <c r="M19" s="28">
-        <v>0.60874506853999999</v>
-      </c>
-      <c r="N19" s="16">
+      <c r="D19" s="12">
+        <v>1849</v>
+      </c>
+      <c r="E19" s="12">
+        <v>1726.909090909091</v>
+      </c>
+      <c r="F19" s="12">
+        <v>122.09090909090909</v>
+      </c>
+      <c r="G19" s="19">
+        <v>96.090909090909093</v>
+      </c>
+      <c r="H19" s="12">
+        <v>44.545454545454547</v>
+      </c>
+      <c r="I19" s="12">
+        <v>51.545454545454547</v>
+      </c>
+      <c r="J19" s="13">
+        <v>60.363636363636367</v>
+      </c>
+      <c r="K19" s="12">
+        <v>44.545454545454547</v>
+      </c>
+      <c r="L19" s="12">
+        <v>15.818181818181818</v>
+      </c>
+      <c r="M19" s="20">
+        <v>0.61559422054545454</v>
+      </c>
+      <c r="N19" s="11">
         <v>1</v>
       </c>
-      <c r="O19" s="16">
-        <v>0.31021478029999999</v>
-      </c>
-      <c r="P19" s="28">
-        <v>0.031553363699999996</v>
-      </c>
-      <c r="Q19" s="16">
-        <v>0.024501073959999998</v>
-      </c>
-      <c r="R19" s="16">
-        <v>0.12991856737999999</v>
-      </c>
-    </row>
-    <row r="20">
+      <c r="O19" s="11">
+        <v>0.30664508818181824</v>
+      </c>
+      <c r="P19" s="20">
+        <v>3.2510241000000002E-2</v>
+      </c>
+      <c r="Q19" s="11">
+        <v>2.5630543545454545E-2</v>
+      </c>
+      <c r="R19" s="11">
+        <v>0.12948781645454546</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>24</v>
       </c>
       <c r="B20" t="s">
         <v>30</v>
       </c>
-      <c r="C20" s="17">
+      <c r="C20" s="12">
         <v>2280.0149253731342</v>
       </c>
-      <c r="D20" s="17">
-        <v>1659.0298507462687</v>
-      </c>
-      <c r="E20" s="17">
-        <v>1539.2835820895523</v>
-      </c>
-      <c r="F20" s="17">
-        <v>119.74626865671642</v>
-      </c>
-      <c r="G20" s="27">
-        <v>84.164179104477611</v>
-      </c>
-      <c r="H20" s="17">
-        <v>39.537313432835823</v>
-      </c>
-      <c r="I20" s="17">
-        <v>44.626865671641788</v>
-      </c>
-      <c r="J20" s="18">
-        <v>57.089552238805972</v>
-      </c>
-      <c r="K20" s="17">
-        <v>39.447761194029852</v>
-      </c>
-      <c r="L20" s="17">
-        <v>17.64179104477612</v>
-      </c>
-      <c r="M20" s="28">
-        <v>0.67111925169503484</v>
-      </c>
-      <c r="N20" s="16">
-        <v>0.9978259031717881</v>
-      </c>
-      <c r="O20" s="16">
-        <v>0.40751664498032786</v>
-      </c>
-      <c r="P20" s="28">
-        <v>0.034216342143979193</v>
-      </c>
-      <c r="Q20" s="16">
-        <v>0.025361137413804972</v>
-      </c>
-      <c r="R20" s="16">
-        <v>0.14829993323752425</v>
-      </c>
-    </row>
-    <row r="22">
+      <c r="D20" s="12">
+        <v>1741.23</v>
+      </c>
+      <c r="E20" s="12">
+        <v>1620.39</v>
+      </c>
+      <c r="F20" s="12">
+        <v>120.84</v>
+      </c>
+      <c r="G20" s="19">
+        <v>88.51</v>
+      </c>
+      <c r="H20" s="12">
+        <v>40.86</v>
+      </c>
+      <c r="I20" s="12">
+        <v>47.65</v>
+      </c>
+      <c r="J20" s="13">
+        <v>58.1</v>
+      </c>
+      <c r="K20" s="12">
+        <v>40.799999999999997</v>
+      </c>
+      <c r="L20" s="12">
+        <v>17.3</v>
+      </c>
+      <c r="M20" s="20">
+        <v>0.64858743598567326</v>
+      </c>
+      <c r="N20" s="11">
+        <v>0.99854335512509795</v>
+      </c>
+      <c r="O20" s="11">
+        <v>0.37269075122681977</v>
+      </c>
+      <c r="P20" s="20">
+        <v>3.334804027646604E-2</v>
+      </c>
+      <c r="Q20" s="11">
+        <v>2.5081891327249344E-2</v>
+      </c>
+      <c r="R20" s="11">
+        <v>0.1438161725791412</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>27</v>
       </c>
       <c r="B22" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="17">
+      <c r="C22" s="12">
         <v>2571</v>
       </c>
-      <c r="D22" s="17">
-        <v>1843.0599999999999</v>
-      </c>
-      <c r="E22" s="17">
-        <v>1720.3800000000001</v>
-      </c>
-      <c r="F22" s="17">
-        <v>122.68000000000001</v>
-      </c>
-      <c r="G22" s="27">
-        <v>347.60000000000002</v>
-      </c>
-      <c r="H22" s="17">
-        <v>235.90000000000001</v>
-      </c>
-      <c r="I22" s="17">
-        <v>111.7</v>
-      </c>
-      <c r="J22" s="18">
-        <v>264.39999999999998</v>
-      </c>
-      <c r="K22" s="17">
-        <v>234.47999999999999</v>
-      </c>
-      <c r="L22" s="17">
-        <v>29.920000000000002</v>
-      </c>
-      <c r="M22" s="28">
+      <c r="D22" s="12">
+        <v>1825.8181818181818</v>
+      </c>
+      <c r="E22" s="12">
+        <v>1702.2727272727273</v>
+      </c>
+      <c r="F22" s="12">
+        <v>123.54545454545455</v>
+      </c>
+      <c r="G22" s="19">
+        <v>343.81818181818181</v>
+      </c>
+      <c r="H22" s="12">
+        <v>229.45454545454547</v>
+      </c>
+      <c r="I22" s="12">
+        <v>114.36363636363636</v>
+      </c>
+      <c r="J22" s="13">
+        <v>260.27272727272725</v>
+      </c>
+      <c r="K22" s="12">
+        <v>228.09090909090909</v>
+      </c>
+      <c r="L22" s="12">
+        <v>32.18181818181818</v>
+      </c>
+      <c r="M22" s="20">
         <v>0.75477757894000008</v>
       </c>
-      <c r="N22" s="16">
+      <c r="N22" s="11">
         <v>0.99424652603999975</v>
       </c>
-      <c r="O22" s="16">
-        <v>0.26821496087999996</v>
-      </c>
-      <c r="P22" s="28">
+      <c r="O22" s="11">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="P22" s="20">
         <v>0.14306746273999998</v>
       </c>
-      <c r="Q22" s="16">
-        <v>0.13580868495999998</v>
-      </c>
-      <c r="R22" s="16">
-        <v>0.24375225096</v>
-      </c>
-    </row>
-    <row r="23">
+      <c r="Q22" s="11">
+        <v>0.13</v>
+      </c>
+      <c r="R22" s="11">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>27</v>
       </c>
       <c r="B23" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="17">
+      <c r="C23" s="12">
         <v>2313.3384615384616</v>
       </c>
-      <c r="D23" s="17">
-        <v>1689.2</v>
-      </c>
-      <c r="E23" s="17">
-        <v>1569.5999999999999</v>
-      </c>
-      <c r="F23" s="17">
-        <v>119.59999999999999</v>
-      </c>
-      <c r="G23" s="27">
-        <v>319.01538461538462</v>
-      </c>
-      <c r="H23" s="17">
-        <v>209.96923076923076</v>
-      </c>
-      <c r="I23" s="17">
-        <v>109.04615384615384</v>
-      </c>
-      <c r="J23" s="18">
-        <v>246.7076923076923</v>
-      </c>
-      <c r="K23" s="17">
-        <v>208.7076923076923</v>
-      </c>
-      <c r="L23" s="17">
-        <v>38</v>
-      </c>
-      <c r="M23" s="28">
-        <v>0.76731095004010663</v>
-      </c>
-      <c r="N23" s="16">
-        <v>0.99367655561730406</v>
-      </c>
-      <c r="O23" s="16">
-        <v>0.35008289146787958</v>
-      </c>
-      <c r="P23" s="28">
-        <v>0.14562373004084192</v>
-      </c>
-      <c r="Q23" s="16">
-        <v>0.13243921598739714</v>
-      </c>
-      <c r="R23" s="16">
-        <v>0.31844671912075073</v>
+      <c r="D23" s="12">
+        <v>1686.25</v>
+      </c>
+      <c r="E23" s="12">
+        <v>1566.31</v>
+      </c>
+      <c r="F23" s="12">
+        <v>119.94</v>
+      </c>
+      <c r="G23" s="19">
+        <v>313.7</v>
+      </c>
+      <c r="H23" s="12">
+        <v>202.53</v>
+      </c>
+      <c r="I23" s="12">
+        <v>111.17</v>
+      </c>
+      <c r="J23" s="13">
+        <v>239.78</v>
+      </c>
+      <c r="K23" s="12">
+        <v>201.32</v>
+      </c>
+      <c r="L23" s="12">
+        <v>38.46</v>
+      </c>
+      <c r="M23" s="20">
+        <v>0.77607947889249318</v>
+      </c>
+      <c r="N23" s="11">
+        <v>0.9947966358367587</v>
+      </c>
+      <c r="O23" s="11">
+        <v>0.35931505612732839</v>
+      </c>
+      <c r="P23" s="20">
+        <v>0.14622601831204285</v>
+      </c>
+      <c r="Q23" s="11">
+        <v>0.13317594727024695</v>
+      </c>
+      <c r="R23" s="11">
+        <v>0.31623919512431353</v>
       </c>
     </row>
   </sheetData>
@@ -2506,117 +2233,117 @@
     <mergeCell ref="A4:P4"/>
     <mergeCell ref="A15:P15"/>
   </mergeCells>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:R23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col customWidth="1" min="3" max="6" width="9.00390625"/>
-    <col customWidth="1" min="7" max="7" style="19" width="13.75390625"/>
-    <col customWidth="1" min="8" max="9" width="9.00390625"/>
-    <col customWidth="1" min="10" max="10" style="19" width="16.75390625"/>
-    <col customWidth="1" min="11" max="12" width="9.00390625"/>
-    <col min="13" max="13" style="20" width="9.00390625"/>
-    <col customWidth="1" min="14" max="14" width="12.875"/>
-    <col customWidth="1" min="15" max="15" width="10.875"/>
-    <col min="16" max="16" style="20" width="9.00390625"/>
+    <col min="3" max="6" width="9" customWidth="1"/>
+    <col min="7" max="7" width="13.77734375" style="14" customWidth="1"/>
+    <col min="8" max="9" width="9" customWidth="1"/>
+    <col min="10" max="10" width="16.77734375" style="14" customWidth="1"/>
+    <col min="11" max="12" width="9" customWidth="1"/>
+    <col min="13" max="13" width="9" style="15"/>
+    <col min="14" max="14" width="12.88671875" customWidth="1"/>
+    <col min="15" max="15" width="10.88671875" style="11" customWidth="1"/>
+    <col min="16" max="16" width="9" style="20"/>
+    <col min="17" max="18" width="8.88671875" style="11"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="D1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="21" t="s">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="D1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-    </row>
-    <row r="2" ht="28" customHeight="1">
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+    </row>
+    <row r="2" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="22" t="s">
+      <c r="G2" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="34" t="s">
+      <c r="J2" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="L2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="23" t="s">
+      <c r="M2" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="N2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="O2" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="P2" s="24" t="s">
+      <c r="P2" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="Q2" s="12" t="s">
+      <c r="Q2" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="R2" s="12" t="s">
+      <c r="R2" s="42" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="13" t="s">
+    <row r="4" spans="1:18" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13"/>
-      <c r="M4" s="26"/>
-      <c r="N4" s="13"/>
-      <c r="O4" s="13"/>
-      <c r="P4" s="26"/>
-    </row>
-    <row r="5">
+      <c r="B4" s="32"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="32"/>
+      <c r="J4" s="35"/>
+      <c r="K4" s="32"/>
+      <c r="L4" s="32"/>
+      <c r="M4" s="36"/>
+      <c r="N4" s="32"/>
+      <c r="O4" s="32"/>
+      <c r="P4" s="36"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -2626,53 +2353,53 @@
       <c r="C5">
         <v>1331</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="12">
         <v>1143.6600000000001</v>
       </c>
-      <c r="E5">
-        <v>1110.9300000000001</v>
-      </c>
-      <c r="F5">
+      <c r="E5" s="12">
+        <v>1110.93</v>
+      </c>
+      <c r="F5" s="12">
         <v>32.729999999999997</v>
       </c>
       <c r="G5" s="19">
         <v>1167.54</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="12">
         <v>1131.73</v>
       </c>
-      <c r="I5">
-        <v>35.810000000000002</v>
+      <c r="I5" s="12">
+        <v>35.81</v>
       </c>
       <c r="J5" s="19">
         <v>1046.46</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="12">
         <v>1031.95</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="12">
         <v>14.51</v>
       </c>
       <c r="M5" s="20">
         <v>0.89647425028660721</v>
       </c>
-      <c r="N5" s="16">
+      <c r="N5" s="11">
         <v>0.91269452633283421</v>
       </c>
-      <c r="O5" s="16">
+      <c r="O5" s="11">
         <v>0.40988859384234111</v>
       </c>
       <c r="P5" s="20">
         <v>0.91462287869256131</v>
       </c>
-      <c r="Q5" s="16">
+      <c r="Q5" s="11">
         <v>0.92816112779701487</v>
       </c>
-      <c r="R5" s="16">
+      <c r="R5" s="11">
         <v>0.42304233970138955</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -2682,165 +2409,165 @@
       <c r="C6">
         <v>1000</v>
       </c>
-      <c r="D6">
-        <v>860.00999999999999</v>
-      </c>
-      <c r="E6">
-        <v>835.39999999999998</v>
-      </c>
-      <c r="F6">
-        <v>24.609999999999999</v>
+      <c r="D6" s="12">
+        <v>860.01</v>
+      </c>
+      <c r="E6" s="12">
+        <v>835.4</v>
+      </c>
+      <c r="F6" s="12">
+        <v>24.61</v>
       </c>
       <c r="G6" s="19">
-        <v>875.97000000000003</v>
-      </c>
-      <c r="H6">
-        <v>848.03999999999996</v>
-      </c>
-      <c r="I6">
+        <v>875.97</v>
+      </c>
+      <c r="H6" s="12">
+        <v>848.04</v>
+      </c>
+      <c r="I6" s="12">
         <v>27.93</v>
       </c>
       <c r="J6" s="19">
-        <v>785.09000000000003</v>
-      </c>
-      <c r="K6">
-        <v>774.22000000000003</v>
-      </c>
-      <c r="L6">
-        <v>10.869999999999999</v>
+        <v>785.09</v>
+      </c>
+      <c r="K6" s="12">
+        <v>774.22</v>
+      </c>
+      <c r="L6" s="12">
+        <v>10.87</v>
       </c>
       <c r="M6" s="20">
         <v>0.89630563775804961</v>
       </c>
-      <c r="N6">
+      <c r="N6" s="11">
         <v>0.91375401284577051</v>
       </c>
-      <c r="O6">
+      <c r="O6" s="11">
         <v>0.40113933619079611</v>
       </c>
       <c r="P6" s="20">
         <v>0.91242104756811282</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" s="11">
         <v>0.9260037517430425</v>
       </c>
-      <c r="R6">
+      <c r="R6" s="11">
         <v>0.41841437703592887</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>24</v>
       </c>
       <c r="B8" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="35">
+      <c r="C8" s="27">
         <v>1331</v>
       </c>
-      <c r="D8" s="35">
+      <c r="D8" s="37">
         <v>1143.6600000000001</v>
       </c>
-      <c r="E8" s="35">
-        <v>1110.9300000000001</v>
-      </c>
-      <c r="F8" s="35">
+      <c r="E8" s="37">
+        <v>1110.93</v>
+      </c>
+      <c r="F8" s="37">
         <v>32.729999999999997</v>
       </c>
-      <c r="G8" s="36">
+      <c r="G8" s="38">
         <v>1219.79</v>
       </c>
-      <c r="H8" s="35">
+      <c r="H8" s="37">
         <v>1172.05</v>
       </c>
-      <c r="I8" s="35">
-        <v>47.740000000000002</v>
-      </c>
-      <c r="J8" s="36">
+      <c r="I8" s="37">
+        <v>47.74</v>
+      </c>
+      <c r="J8" s="38">
         <v>1080.3499999999999</v>
       </c>
-      <c r="K8" s="35">
+      <c r="K8" s="37">
         <v>1061.71</v>
       </c>
-      <c r="L8" s="35">
-        <v>18.640000000000001</v>
-      </c>
-      <c r="M8" s="37">
+      <c r="L8" s="37">
+        <v>18.64</v>
+      </c>
+      <c r="M8" s="39">
         <v>0.88569130016964803</v>
       </c>
-      <c r="N8" s="16">
+      <c r="N8" s="11">
         <v>0.90648625838723873</v>
       </c>
-      <c r="O8" s="16">
+      <c r="O8" s="11">
         <v>0.39627604911469866</v>
       </c>
-      <c r="P8" s="37">
+      <c r="P8" s="39">
         <v>0.94438776389571188</v>
       </c>
-      <c r="Q8" s="38">
+      <c r="Q8" s="28">
         <v>0.95520802465734078</v>
       </c>
-      <c r="R8" s="38">
+      <c r="R8" s="28">
         <v>0.54836554643792279</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>24</v>
       </c>
       <c r="B9" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="35">
+      <c r="C9" s="27">
         <v>1000</v>
       </c>
-      <c r="D9" s="35">
-        <v>860.00999999999999</v>
-      </c>
-      <c r="E9" s="35">
-        <v>835.39999999999998</v>
-      </c>
-      <c r="F9" s="35">
-        <v>24.609999999999999</v>
-      </c>
-      <c r="G9" s="36">
+      <c r="D9" s="37">
+        <v>860.01</v>
+      </c>
+      <c r="E9" s="37">
+        <v>835.4</v>
+      </c>
+      <c r="F9" s="37">
+        <v>24.61</v>
+      </c>
+      <c r="G9" s="38">
         <v>916.12</v>
       </c>
-      <c r="H9" s="35">
-        <v>878.67999999999995</v>
-      </c>
-      <c r="I9" s="35">
-        <v>37.439999999999998</v>
-      </c>
-      <c r="J9" s="36">
-        <v>811.97000000000003</v>
-      </c>
-      <c r="K9" s="35">
-        <v>797.79999999999995</v>
-      </c>
-      <c r="L9" s="35">
+      <c r="H9" s="37">
+        <v>878.68</v>
+      </c>
+      <c r="I9" s="37">
+        <v>37.44</v>
+      </c>
+      <c r="J9" s="38">
+        <v>811.97</v>
+      </c>
+      <c r="K9" s="37">
+        <v>797.8</v>
+      </c>
+      <c r="L9" s="37">
         <v>14.17</v>
       </c>
-      <c r="M9" s="37">
+      <c r="M9" s="39">
         <v>0.88623349182234035</v>
       </c>
-      <c r="N9" s="35">
+      <c r="N9" s="28">
         <v>0.90855050698943884</v>
       </c>
-      <c r="O9" s="35">
+      <c r="O9" s="28">
         <v>0.3902462559028726</v>
       </c>
-      <c r="P9" s="37">
+      <c r="P9" s="39">
         <v>0.94383165349221299</v>
       </c>
-      <c r="Q9" s="35">
+      <c r="Q9" s="28">
         <v>0.95449551222090745</v>
       </c>
-      <c r="R9" s="35">
+      <c r="R9" s="28">
         <v>0.55833567435556519</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -2850,53 +2577,53 @@
       <c r="C11">
         <v>1331</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="12">
         <v>1143.6600000000001</v>
       </c>
-      <c r="E11">
-        <v>1110.9300000000001</v>
-      </c>
-      <c r="F11">
+      <c r="E11" s="12">
+        <v>1110.93</v>
+      </c>
+      <c r="F11" s="12">
         <v>32.729999999999997</v>
       </c>
       <c r="G11" s="19">
         <v>1246.99</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="12">
         <v>1191.21</v>
       </c>
-      <c r="I11">
-        <v>55.780000000000001</v>
+      <c r="I11" s="12">
+        <v>55.78</v>
       </c>
       <c r="J11" s="19">
         <v>1097.3599999999999</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="12">
         <v>1075.8699999999999</v>
       </c>
-      <c r="L11">
-        <v>21.489999999999998</v>
+      <c r="L11" s="12">
+        <v>21.49</v>
       </c>
       <c r="M11" s="20">
         <v>0.87995955565741213</v>
       </c>
-      <c r="N11" s="16">
+      <c r="N11" s="11">
         <v>0.90370861417927495</v>
       </c>
-      <c r="O11" s="16">
+      <c r="O11" s="11">
         <v>0.39229369924488566</v>
       </c>
       <c r="P11" s="20">
         <v>0.9593259602906502</v>
       </c>
-      <c r="Q11" s="16">
+      <c r="Q11" s="11">
         <v>0.96807912300555798</v>
       </c>
-      <c r="R11" s="16">
+      <c r="R11" s="11">
         <v>0.63885868280607627</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -2906,73 +2633,73 @@
       <c r="C12">
         <v>1000</v>
       </c>
-      <c r="D12">
-        <v>860.00999999999999</v>
-      </c>
-      <c r="E12">
-        <v>835.39999999999998</v>
-      </c>
-      <c r="F12">
-        <v>24.609999999999999</v>
+      <c r="D12" s="12">
+        <v>860.01</v>
+      </c>
+      <c r="E12" s="12">
+        <v>835.4</v>
+      </c>
+      <c r="F12" s="12">
+        <v>24.61</v>
       </c>
       <c r="G12" s="19">
-        <v>935.54999999999995</v>
-      </c>
-      <c r="H12">
-        <v>892.49000000000001</v>
-      </c>
-      <c r="I12">
-        <v>43.060000000000002</v>
+        <v>935.55</v>
+      </c>
+      <c r="H12" s="12">
+        <v>892.49</v>
+      </c>
+      <c r="I12" s="12">
+        <v>43.06</v>
       </c>
       <c r="J12" s="19">
-        <v>823.97000000000003</v>
-      </c>
-      <c r="K12">
-        <v>807.89999999999998</v>
-      </c>
-      <c r="L12">
+        <v>823.97</v>
+      </c>
+      <c r="K12" s="12">
+        <v>807.9</v>
+      </c>
+      <c r="L12" s="12">
         <v>16.07</v>
       </c>
       <c r="M12" s="20">
         <v>0.88062997075140315</v>
       </c>
-      <c r="N12">
+      <c r="N12" s="11">
         <v>0.90573898321663482</v>
       </c>
-      <c r="O12">
+      <c r="O12" s="11">
         <v>0.38159625285665327</v>
       </c>
       <c r="P12" s="20">
         <v>0.95786074677211008</v>
       </c>
-      <c r="Q12">
+      <c r="Q12" s="11">
         <v>0.96670956284560672</v>
       </c>
-      <c r="R12">
+      <c r="R12" s="11">
         <v>0.63565432135863864</v>
       </c>
     </row>
-    <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="13" t="s">
+    <row r="15" spans="1:18" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="25"/>
-      <c r="K15" s="13"/>
-      <c r="L15" s="13"/>
-      <c r="M15" s="26"/>
-      <c r="N15" s="13"/>
-      <c r="O15" s="13"/>
-      <c r="P15" s="26"/>
-    </row>
-    <row r="16">
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="35"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="35"/>
+      <c r="K15" s="32"/>
+      <c r="L15" s="32"/>
+      <c r="M15" s="36"/>
+      <c r="N15" s="32"/>
+      <c r="O15" s="32"/>
+      <c r="P15" s="36"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -2982,53 +2709,53 @@
       <c r="C16">
         <v>2571</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="12">
         <v>2354.96</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="12">
         <v>2326.29</v>
       </c>
-      <c r="F16">
-        <v>28.670000000000002</v>
+      <c r="F16" s="12">
+        <v>28.67</v>
       </c>
       <c r="G16" s="19">
         <v>2405.04</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="12">
         <v>2366.7800000000002</v>
       </c>
-      <c r="I16">
-        <v>38.259999999999998</v>
+      <c r="I16" s="12">
+        <v>38.26</v>
       </c>
       <c r="J16" s="19">
-        <v>2252.4200000000001</v>
-      </c>
-      <c r="K16">
+        <v>2252.42</v>
+      </c>
+      <c r="K16" s="12">
         <v>2238.3200000000002</v>
       </c>
-      <c r="L16">
+      <c r="L16" s="12">
         <v>14.1</v>
       </c>
       <c r="M16" s="20">
         <v>0.93655789541389611</v>
       </c>
-      <c r="N16" s="16">
+      <c r="N16" s="11">
         <v>0.94593988179961275</v>
       </c>
-      <c r="O16" s="16">
+      <c r="O16" s="11">
         <v>0.38817437008475791</v>
       </c>
       <c r="P16" s="20">
         <v>0.95627927759889997</v>
       </c>
-      <c r="Q16" s="16">
+      <c r="Q16" s="11">
         <v>0.96193628953336452</v>
       </c>
-      <c r="R16" s="16">
+      <c r="R16" s="11">
         <v>0.4870498275662416</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -3038,53 +2765,65 @@
       <c r="C17">
         <v>1000</v>
       </c>
-      <c r="D17">
-        <v>915.46000000000004</v>
-      </c>
-      <c r="E17">
-        <v>903.99000000000001</v>
-      </c>
-      <c r="F17">
-        <v>11.470000000000001</v>
+      <c r="D17" s="12">
+        <v>915.46</v>
+      </c>
+      <c r="E17" s="12">
+        <v>903.99</v>
+      </c>
+      <c r="F17" s="12">
+        <v>11.47</v>
       </c>
       <c r="G17" s="19">
-        <v>936.10000000000002</v>
-      </c>
-      <c r="H17">
-        <v>920.92999999999995</v>
-      </c>
-      <c r="I17">
+        <v>936.1</v>
+      </c>
+      <c r="H17" s="12">
+        <v>920.93</v>
+      </c>
+      <c r="I17" s="12">
         <v>15.17</v>
       </c>
       <c r="J17" s="19">
-        <v>876.16999999999996</v>
-      </c>
-      <c r="K17">
-        <v>870.33000000000004</v>
-      </c>
-      <c r="L17">
-        <v>5.8399999999999999</v>
+        <v>876.17</v>
+      </c>
+      <c r="K17" s="12">
+        <v>870.33</v>
+      </c>
+      <c r="L17" s="12">
+        <v>5.84</v>
       </c>
       <c r="M17" s="20">
         <v>0.93600696530829586</v>
       </c>
-      <c r="N17">
+      <c r="N17" s="11">
         <v>0.94525940591592372</v>
       </c>
-      <c r="O17">
+      <c r="O17" s="11">
         <v>0.38565112493453341</v>
       </c>
       <c r="P17" s="20">
         <v>0.95695398868112902</v>
       </c>
-      <c r="Q17">
+      <c r="Q17" s="11">
         <v>0.96256816397111133</v>
       </c>
-      <c r="R17">
+      <c r="R17" s="11">
         <v>0.47844516425080419</v>
       </c>
     </row>
-    <row r="19">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="12"/>
+      <c r="M18" s="20"/>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -3094,53 +2833,53 @@
       <c r="C19">
         <v>2571</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="12">
         <v>2354.96</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="12">
         <v>2326.29</v>
       </c>
-      <c r="F19">
-        <v>28.670000000000002</v>
+      <c r="F19" s="12">
+        <v>28.67</v>
       </c>
       <c r="G19" s="19">
         <v>2454.79</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="12">
         <v>2405.27</v>
       </c>
-      <c r="I19">
-        <v>49.520000000000003</v>
+      <c r="I19" s="12">
+        <v>49.52</v>
       </c>
       <c r="J19" s="19">
         <v>2286.7399999999998</v>
       </c>
-      <c r="K19">
+      <c r="K19" s="12">
         <v>2269.46</v>
       </c>
-      <c r="L19">
-        <v>17.280000000000001</v>
+      <c r="L19" s="12">
+        <v>17.28</v>
       </c>
       <c r="M19" s="20">
         <v>0.93150652982465443</v>
       </c>
-      <c r="N19" s="16">
+      <c r="N19" s="11">
         <v>0.94370073256047027</v>
       </c>
-      <c r="O19" s="16">
+      <c r="O19" s="11">
         <v>0.37053375707013869</v>
       </c>
       <c r="P19" s="20">
         <v>0.97090784893787263</v>
       </c>
-      <c r="Q19" s="16">
+      <c r="Q19" s="11">
         <v>0.97540056429877242</v>
       </c>
-      <c r="R19" s="16">
+      <c r="R19" s="11">
         <v>0.59981864189732481</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>24</v>
       </c>
@@ -3150,53 +2889,65 @@
       <c r="C20">
         <v>1000</v>
       </c>
-      <c r="D20">
-        <v>915.46000000000004</v>
-      </c>
-      <c r="E20">
-        <v>903.99000000000001</v>
-      </c>
-      <c r="F20">
-        <v>11.470000000000001</v>
+      <c r="D20" s="12">
+        <v>915.46</v>
+      </c>
+      <c r="E20" s="12">
+        <v>903.99</v>
+      </c>
+      <c r="F20" s="12">
+        <v>11.47</v>
       </c>
       <c r="G20" s="19">
-        <v>955.27999999999997</v>
-      </c>
-      <c r="H20">
-        <v>935.92999999999995</v>
-      </c>
-      <c r="I20">
+        <v>955.28</v>
+      </c>
+      <c r="H20" s="12">
+        <v>935.93</v>
+      </c>
+      <c r="I20" s="12">
         <v>19.350000000000001</v>
       </c>
       <c r="J20" s="19">
-        <v>889.13999999999999</v>
-      </c>
-      <c r="K20">
-        <v>882.09000000000003</v>
-      </c>
-      <c r="L20">
-        <v>7.0499999999999998</v>
+        <v>889.14</v>
+      </c>
+      <c r="K20" s="12">
+        <v>882.09</v>
+      </c>
+      <c r="L20" s="12">
+        <v>7.05</v>
       </c>
       <c r="M20" s="20">
         <v>0.93075051502819095</v>
       </c>
-      <c r="N20">
+      <c r="N20" s="11">
         <v>0.94264040522161507</v>
       </c>
-      <c r="O20">
+      <c r="O20" s="11">
         <v>0.37312676737748901</v>
       </c>
       <c r="P20" s="20">
         <v>0.97115500563222024</v>
       </c>
-      <c r="Q20">
+      <c r="Q20" s="11">
         <v>0.9756320816261852</v>
       </c>
-      <c r="R20">
+      <c r="R20" s="11">
         <v>0.58690458807468837</v>
       </c>
     </row>
-    <row r="22">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="19"/>
+      <c r="K21" s="12"/>
+      <c r="L21" s="12"/>
+      <c r="M21" s="20"/>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>27</v>
       </c>
@@ -3206,53 +2957,53 @@
       <c r="C22">
         <v>2571</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="12">
         <v>2354.96</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="12">
         <v>2326.29</v>
       </c>
-      <c r="F22">
-        <v>28.670000000000002</v>
+      <c r="F22" s="12">
+        <v>28.67</v>
       </c>
       <c r="G22" s="19">
-        <v>2482.1700000000001</v>
-      </c>
-      <c r="H22">
-        <v>2425.0599999999999</v>
-      </c>
-      <c r="I22">
-        <v>57.109999999999999</v>
+        <v>2482.17</v>
+      </c>
+      <c r="H22" s="12">
+        <v>2425.06</v>
+      </c>
+      <c r="I22" s="12">
+        <v>57.11</v>
       </c>
       <c r="J22" s="19">
         <v>2304.4499999999998</v>
       </c>
-      <c r="K22">
-        <v>2284.9200000000001</v>
-      </c>
-      <c r="L22">
-        <v>19.530000000000001</v>
+      <c r="K22" s="12">
+        <v>2284.92</v>
+      </c>
+      <c r="L22" s="12">
+        <v>19.53</v>
       </c>
       <c r="M22" s="20">
         <v>0.92835083465222401</v>
       </c>
-      <c r="N22" s="16">
+      <c r="N22" s="11">
         <v>0.94235107793660389</v>
       </c>
-      <c r="O22" s="16">
+      <c r="O22" s="11">
         <v>0.3620199063806267</v>
       </c>
       <c r="P22" s="20">
         <v>0.97845790673565081</v>
       </c>
-      <c r="Q22" s="16">
+      <c r="Q22" s="11">
         <v>0.98208784389422799</v>
       </c>
-      <c r="R22" s="16">
+      <c r="R22" s="11">
         <v>0.67982831522213616</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>27</v>
       </c>
@@ -3262,49 +3013,49 @@
       <c r="C23">
         <v>1000</v>
       </c>
-      <c r="D23">
-        <v>915.46000000000004</v>
-      </c>
-      <c r="E23">
-        <v>903.99000000000001</v>
-      </c>
-      <c r="F23">
-        <v>11.470000000000001</v>
+      <c r="D23" s="12">
+        <v>915.46</v>
+      </c>
+      <c r="E23" s="12">
+        <v>903.99</v>
+      </c>
+      <c r="F23" s="12">
+        <v>11.47</v>
       </c>
       <c r="G23" s="19">
-        <v>965.76999999999998</v>
-      </c>
-      <c r="H23">
-        <v>943.47000000000003</v>
-      </c>
-      <c r="I23">
-        <v>22.300000000000001</v>
+        <v>965.77</v>
+      </c>
+      <c r="H23" s="12">
+        <v>943.47</v>
+      </c>
+      <c r="I23" s="12">
+        <v>22.3</v>
       </c>
       <c r="J23" s="19">
-        <v>896.03999999999996</v>
-      </c>
-      <c r="K23">
-        <v>888.07000000000005</v>
-      </c>
-      <c r="L23">
-        <v>7.9699999999999998</v>
+        <v>896.04</v>
+      </c>
+      <c r="K23" s="12">
+        <v>888.07</v>
+      </c>
+      <c r="L23" s="12">
+        <v>7.97</v>
       </c>
       <c r="M23" s="20">
         <v>0.92776836160630327</v>
       </c>
-      <c r="N23">
+      <c r="N23" s="11">
         <v>0.94142581555162619</v>
       </c>
-      <c r="O23">
+      <c r="O23" s="11">
         <v>0.37265765544772272</v>
       </c>
       <c r="P23" s="20">
         <v>0.97870869641812563</v>
       </c>
-      <c r="Q23">
+      <c r="Q23" s="11">
         <v>0.98227446908744143</v>
       </c>
-      <c r="R23">
+      <c r="R23" s="11">
         <v>0.67235678095442164</v>
       </c>
     </row>
@@ -3315,9 +3066,7 @@
     <mergeCell ref="A4:P4"/>
     <mergeCell ref="A15:P15"/>
   </mergeCells>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
--- a/EX1/Baseline_prediction_posteriors/EX1_baseline_effectiveness_all_models.xlsx
+++ b/EX1/Baseline_prediction_posteriors/EX1_baseline_effectiveness_all_models.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xhulj\Desktop\CPa\EX1\Baseline_prediction_posteriors\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84CF189C-B17C-499C-96FE-5C47999A7F9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90C895DF-F3AB-4929-9DA4-B508AFE41223}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19940" yWindow="3340" windowWidth="17280" windowHeight="8880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LApredict" sheetId="1" r:id="rId1"/>
@@ -134,9 +134,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
@@ -281,7 +280,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -328,13 +327,23 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -358,18 +367,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -619,16 +616,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="D1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="30" t="s">
+      <c r="D1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
     </row>
     <row r="2" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -687,24 +684,24 @@
       </c>
     </row>
     <row r="4" spans="1:18" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="32" t="s">
+      <c r="A4" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="32"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="33"/>
-      <c r="H4" s="32"/>
-      <c r="I4" s="32"/>
-      <c r="J4" s="33"/>
-      <c r="K4" s="32"/>
-      <c r="L4" s="32"/>
-      <c r="M4" s="32"/>
-      <c r="N4" s="32"/>
-      <c r="O4" s="32"/>
-      <c r="P4" s="32"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="37"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="36"/>
+      <c r="J4" s="37"/>
+      <c r="K4" s="36"/>
+      <c r="L4" s="36"/>
+      <c r="M4" s="36"/>
+      <c r="N4" s="36"/>
+      <c r="O4" s="36"/>
+      <c r="P4" s="36"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
@@ -746,10 +743,10 @@
       <c r="M5" s="10">
         <v>0.94594594594594583</v>
       </c>
-      <c r="N5">
+      <c r="N5" s="11">
         <v>0.95402298850574696</v>
       </c>
-      <c r="O5">
+      <c r="O5" s="11">
         <v>0.81818181818181823</v>
       </c>
       <c r="P5" s="10">
@@ -802,25 +799,29 @@
       <c r="M6" s="10">
         <v>0.95589590919754097</v>
       </c>
-      <c r="N6">
+      <c r="N6" s="11">
         <v>0.96837903382638491</v>
       </c>
-      <c r="O6">
+      <c r="O6" s="11">
         <v>0.53497536945812807</v>
       </c>
       <c r="P6" s="10">
         <v>7.3359030914489115E-2</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" s="11">
         <v>7.7957299123665752E-2</v>
       </c>
-      <c r="R6">
+      <c r="R6" s="11">
         <v>1.458962348005291E-2</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="M7" s="10"/>
+      <c r="N7" s="11"/>
+      <c r="O7" s="11"/>
       <c r="P7" s="10"/>
+      <c r="Q7" s="11"/>
+      <c r="R7" s="11"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
@@ -862,10 +863,10 @@
       <c r="M8" s="10">
         <v>0.92405063291139222</v>
       </c>
-      <c r="N8">
+      <c r="N8" s="11">
         <v>0.93013100436681218</v>
       </c>
-      <c r="O8">
+      <c r="O8" s="11">
         <v>0.75</v>
       </c>
       <c r="P8" s="10">
@@ -900,43 +901,52 @@
       <c r="G9" s="13">
         <v>205.18390804597701</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="12">
         <v>198.81609195402299</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="12">
         <v>6.3678160919540234</v>
       </c>
-      <c r="J9" s="1">
+      <c r="J9" s="13">
         <v>190.86206896551724</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="12">
         <v>186.75862068965517</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="12">
         <v>4.1034482758620694</v>
       </c>
       <c r="M9" s="10">
         <v>0.93024130642327951</v>
       </c>
-      <c r="N9">
+      <c r="N9" s="11">
         <v>0.93937673519787712</v>
       </c>
-      <c r="O9">
+      <c r="O9" s="11">
         <v>0.66989606817193026</v>
       </c>
       <c r="P9" s="10">
         <v>0.14041214291895668</v>
       </c>
-      <c r="Q9">
+      <c r="Q9" s="11">
         <v>0.14816037180233008</v>
       </c>
-      <c r="R9">
+      <c r="R9" s="11">
         <v>4.1299047689924567E-2</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="12"/>
+      <c r="L10" s="12"/>
       <c r="M10" s="10"/>
+      <c r="N10" s="11"/>
+      <c r="O10" s="11"/>
       <c r="P10" s="10"/>
+      <c r="Q10" s="11"/>
+      <c r="R10" s="11"/>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
@@ -960,28 +970,28 @@
       <c r="G11" s="1">
         <v>925</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="12">
         <v>900</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="12">
         <v>25</v>
       </c>
-      <c r="J11" s="1">
+      <c r="J11" s="13">
         <v>861</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="12">
         <v>841</v>
       </c>
-      <c r="L11">
+      <c r="L11" s="12">
         <v>20</v>
       </c>
       <c r="M11" s="10">
         <v>0.93081081081081074</v>
       </c>
-      <c r="N11">
+      <c r="N11" s="11">
         <v>0.93444444444444463</v>
       </c>
-      <c r="O11">
+      <c r="O11" s="11">
         <v>0.79999999999999993</v>
       </c>
       <c r="P11" s="10">
@@ -1016,59 +1026,59 @@
       <c r="G12" s="13">
         <v>361.89655172413791</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="12">
         <v>351.80459770114942</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="12">
         <v>10.091954022988507</v>
       </c>
-      <c r="J12" s="1">
+      <c r="J12" s="13">
         <v>327.28735632183907</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="12">
         <v>320.40229885057471</v>
       </c>
-      <c r="L12">
+      <c r="L12" s="12">
         <v>6.8850574712643677</v>
       </c>
       <c r="M12" s="10">
         <v>0.90447429234530075</v>
       </c>
-      <c r="N12">
+      <c r="N12" s="11">
         <v>0.91081797205442516</v>
       </c>
-      <c r="O12">
+      <c r="O12" s="11">
         <v>0.69682391783117736</v>
       </c>
       <c r="P12" s="10">
         <v>0.24080536671930963</v>
       </c>
-      <c r="Q12">
+      <c r="Q12" s="11">
         <v>0.25422548142218399</v>
       </c>
-      <c r="R12">
+      <c r="R12" s="11">
         <v>6.9528877831974464E-2</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="32" t="s">
+      <c r="A15" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="32"/>
-      <c r="C15" s="32"/>
-      <c r="D15" s="32"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="32"/>
-      <c r="G15" s="33"/>
-      <c r="H15" s="32"/>
-      <c r="I15" s="32"/>
-      <c r="J15" s="33"/>
-      <c r="K15" s="32"/>
-      <c r="L15" s="32"/>
-      <c r="M15" s="32"/>
-      <c r="N15" s="32"/>
-      <c r="O15" s="32"/>
-      <c r="P15" s="32"/>
+      <c r="B15" s="36"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="36"/>
+      <c r="F15" s="36"/>
+      <c r="G15" s="37"/>
+      <c r="H15" s="36"/>
+      <c r="I15" s="36"/>
+      <c r="J15" s="37"/>
+      <c r="K15" s="36"/>
+      <c r="L15" s="36"/>
+      <c r="M15" s="36"/>
+      <c r="N15" s="36"/>
+      <c r="O15" s="36"/>
+      <c r="P15" s="36"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
@@ -1110,10 +1120,10 @@
       <c r="M16" s="10">
         <v>0.90196078431372562</v>
       </c>
-      <c r="N16">
+      <c r="N16" s="11">
         <v>0.92000000000000015</v>
       </c>
-      <c r="O16">
+      <c r="O16" s="11">
         <v>0</v>
       </c>
       <c r="P16" s="10">
@@ -1122,7 +1132,7 @@
       <c r="Q16" s="11">
         <v>1.1489936674755636E-2</v>
       </c>
-      <c r="R16">
+      <c r="R16" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1148,43 +1158,52 @@
       <c r="G17" s="1">
         <v>31.04</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="12">
         <v>30.55</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="12">
         <v>0.49</v>
       </c>
-      <c r="J17" s="1">
+      <c r="J17" s="13">
         <v>28.89</v>
       </c>
-      <c r="K17">
+      <c r="K17" s="12">
         <v>28.63</v>
       </c>
-      <c r="L17">
+      <c r="L17" s="12">
         <v>0.26</v>
       </c>
       <c r="M17" s="10">
         <v>0.93201322179392621</v>
       </c>
-      <c r="N17">
+      <c r="N17" s="11">
         <v>0.93833192745302185</v>
       </c>
-      <c r="O17">
+      <c r="O17" s="11">
         <v>0.23499999999999999</v>
       </c>
       <c r="P17" s="10">
         <v>1.7874938991986077E-2</v>
       </c>
-      <c r="Q17">
+      <c r="Q17" s="11">
         <v>1.8017936690040214E-2</v>
       </c>
-      <c r="R17">
+      <c r="R17" s="11">
         <v>1.0587552771074794E-2</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="13"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="12"/>
       <c r="M18" s="10"/>
+      <c r="N18" s="11"/>
+      <c r="O18" s="11"/>
       <c r="P18" s="10"/>
+      <c r="Q18" s="11"/>
+      <c r="R18" s="11"/>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
@@ -1208,28 +1227,28 @@
       <c r="G19" s="1">
         <v>1687</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="12">
         <v>1685</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="12">
         <v>2</v>
       </c>
-      <c r="J19" s="1">
+      <c r="J19" s="13">
         <v>1561</v>
       </c>
-      <c r="K19">
+      <c r="K19" s="12">
         <v>1561</v>
       </c>
-      <c r="L19">
+      <c r="L19" s="12">
         <v>0</v>
       </c>
       <c r="M19" s="10">
         <v>0.92531120331950212</v>
       </c>
-      <c r="N19">
+      <c r="N19" s="11">
         <v>0.92640949554896146</v>
       </c>
-      <c r="O19">
+      <c r="O19" s="11">
         <v>0</v>
       </c>
       <c r="P19" s="10">
@@ -1238,7 +1257,7 @@
       <c r="Q19" s="11">
         <v>0.38990850324551196</v>
       </c>
-      <c r="R19">
+      <c r="R19" s="11">
         <v>0</v>
       </c>
     </row>
@@ -1264,43 +1283,52 @@
       <c r="G20" s="1">
         <v>692.2</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="12">
         <v>691.13</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="12">
         <v>1.07</v>
       </c>
-      <c r="J20" s="1">
+      <c r="J20" s="13">
         <v>641.09</v>
       </c>
-      <c r="K20">
+      <c r="K20" s="12">
         <v>640.45000000000005</v>
       </c>
-      <c r="L20">
+      <c r="L20" s="12">
         <v>0.64</v>
       </c>
       <c r="M20" s="10">
         <v>0.92637758387128288</v>
       </c>
-      <c r="N20">
+      <c r="N20" s="11">
         <v>0.92687939310530154</v>
       </c>
-      <c r="O20">
+      <c r="O20" s="11">
         <v>0.38850000000000001</v>
       </c>
       <c r="P20" s="10">
         <v>0.39666086047024651</v>
       </c>
-      <c r="Q20">
+      <c r="Q20" s="11">
         <v>0.40304906004926666</v>
       </c>
-      <c r="R20">
+      <c r="R20" s="11">
         <v>2.5936622902027605E-2</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="H21" s="12"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="13"/>
+      <c r="K21" s="12"/>
+      <c r="L21" s="12"/>
       <c r="M21" s="10"/>
+      <c r="N21" s="11"/>
+      <c r="O21" s="11"/>
       <c r="P21" s="10"/>
+      <c r="Q21" s="11"/>
+      <c r="R21" s="11"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
@@ -1324,28 +1352,28 @@
       <c r="G22" s="1">
         <v>3089</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="12">
         <v>3085</v>
       </c>
-      <c r="I22">
+      <c r="I22" s="12">
         <v>4</v>
       </c>
-      <c r="J22" s="1">
+      <c r="J22" s="13">
         <v>2785</v>
       </c>
-      <c r="K22">
+      <c r="K22" s="12">
         <v>2784</v>
       </c>
-      <c r="L22">
+      <c r="L22" s="12">
         <v>1</v>
       </c>
       <c r="M22" s="10">
         <v>0.9015862738750402</v>
       </c>
-      <c r="N22">
+      <c r="N22" s="11">
         <v>0.90243111831442469</v>
       </c>
-      <c r="O22">
+      <c r="O22" s="11">
         <v>0.25</v>
       </c>
       <c r="P22" s="10">
@@ -1380,37 +1408,37 @@
       <c r="G23" s="1">
         <v>1246.8900000000001</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="12">
         <v>1245.1500000000001</v>
       </c>
-      <c r="I23">
+      <c r="I23" s="12">
         <v>1.74</v>
       </c>
-      <c r="J23" s="1">
+      <c r="J23" s="13">
         <v>1128.23</v>
       </c>
-      <c r="K23">
+      <c r="K23" s="12">
         <v>1127.3399999999999</v>
       </c>
-      <c r="L23">
+      <c r="L23" s="12">
         <v>0.89</v>
       </c>
       <c r="M23" s="10">
         <v>0.90489731188596967</v>
       </c>
-      <c r="N23">
+      <c r="N23" s="11">
         <v>0.90544552828692626</v>
       </c>
-      <c r="O23">
+      <c r="O23" s="11">
         <v>0.40016666666666673</v>
       </c>
       <c r="P23" s="10">
         <v>0.69798167731187843</v>
       </c>
-      <c r="Q23">
+      <c r="Q23" s="11">
         <v>0.70936400714902093</v>
       </c>
-      <c r="R23">
+      <c r="R23" s="11">
         <v>3.5518231244896302E-2</v>
       </c>
     </row>
@@ -1444,16 +1472,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="D1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="34" t="s">
+      <c r="D1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
     </row>
     <row r="2" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -1512,24 +1540,24 @@
       </c>
     </row>
     <row r="4" spans="1:18" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="32" t="s">
+      <c r="A4" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="32"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="32"/>
-      <c r="I4" s="32"/>
-      <c r="J4" s="33"/>
-      <c r="K4" s="32"/>
-      <c r="L4" s="32"/>
-      <c r="M4" s="36"/>
-      <c r="N4" s="32"/>
-      <c r="O4" s="32"/>
-      <c r="P4" s="36"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="39"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="36"/>
+      <c r="J4" s="37"/>
+      <c r="K4" s="36"/>
+      <c r="L4" s="36"/>
+      <c r="M4" s="40"/>
+      <c r="N4" s="36"/>
+      <c r="O4" s="36"/>
+      <c r="P4" s="40"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
@@ -1871,24 +1899,24 @@
       <c r="M13" s="20"/>
     </row>
     <row r="15" spans="1:18" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="32" t="s">
+      <c r="A15" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="32"/>
-      <c r="C15" s="32"/>
-      <c r="D15" s="32"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="32"/>
-      <c r="G15" s="35"/>
-      <c r="H15" s="32"/>
-      <c r="I15" s="32"/>
-      <c r="J15" s="33"/>
-      <c r="K15" s="32"/>
-      <c r="L15" s="32"/>
-      <c r="M15" s="36"/>
-      <c r="N15" s="32"/>
-      <c r="O15" s="32"/>
-      <c r="P15" s="36"/>
+      <c r="B15" s="36"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="36"/>
+      <c r="F15" s="36"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="36"/>
+      <c r="I15" s="36"/>
+      <c r="J15" s="37"/>
+      <c r="K15" s="36"/>
+      <c r="L15" s="36"/>
+      <c r="M15" s="40"/>
+      <c r="N15" s="36"/>
+      <c r="O15" s="36"/>
+      <c r="P15" s="40"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
@@ -1927,22 +1955,22 @@
       <c r="L16" s="22">
         <v>0.3</v>
       </c>
-      <c r="M16" s="24">
+      <c r="M16" s="20">
         <v>0.2</v>
       </c>
-      <c r="N16" s="25">
-        <v>0</v>
-      </c>
-      <c r="O16" s="25">
+      <c r="N16" s="11">
+        <v>0</v>
+      </c>
+      <c r="O16" s="11">
         <v>0.2</v>
       </c>
-      <c r="P16" s="24">
+      <c r="P16" s="20">
         <v>1.5938580000000001E-4</v>
       </c>
-      <c r="Q16" s="25">
-        <v>0</v>
-      </c>
-      <c r="R16" s="25">
+      <c r="Q16" s="11">
+        <v>0</v>
+      </c>
+      <c r="R16" s="11">
         <v>2.486912E-3</v>
       </c>
     </row>
@@ -1983,22 +2011,22 @@
       <c r="L17" s="22">
         <v>0.31</v>
       </c>
-      <c r="M17" s="24">
+      <c r="M17" s="20">
         <v>0.23666666667000003</v>
       </c>
-      <c r="N17" s="25">
+      <c r="N17" s="11">
         <v>0.03</v>
       </c>
-      <c r="O17" s="25">
+      <c r="O17" s="11">
         <v>0.20666666667</v>
       </c>
-      <c r="P17" s="24">
+      <c r="P17" s="20">
         <v>2.189483363479058E-4</v>
       </c>
-      <c r="Q17" s="25">
+      <c r="Q17" s="11">
         <v>3.7499999999999997E-5</v>
       </c>
-      <c r="R17" s="25">
+      <c r="R17" s="11">
         <v>2.6219458210068793E-3</v>
       </c>
     </row>
@@ -2256,16 +2284,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="D1" s="29" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="34" t="s">
+      <c r="D1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
     </row>
     <row r="2" spans="1:18" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -2295,7 +2323,7 @@
       <c r="I2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="26" t="s">
+      <c r="J2" s="24" t="s">
         <v>11</v>
       </c>
       <c r="K2" s="2" t="s">
@@ -2310,38 +2338,38 @@
       <c r="N2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="40" t="s">
+      <c r="O2" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="P2" s="41" t="s">
+      <c r="P2" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="Q2" s="42" t="s">
+      <c r="Q2" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="R2" s="42" t="s">
+      <c r="R2" s="32" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="32" t="s">
+      <c r="A4" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="32"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="32"/>
-      <c r="I4" s="32"/>
-      <c r="J4" s="35"/>
-      <c r="K4" s="32"/>
-      <c r="L4" s="32"/>
-      <c r="M4" s="36"/>
-      <c r="N4" s="32"/>
-      <c r="O4" s="32"/>
-      <c r="P4" s="36"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="39"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="36"/>
+      <c r="J4" s="39"/>
+      <c r="K4" s="36"/>
+      <c r="L4" s="36"/>
+      <c r="M4" s="40"/>
+      <c r="N4" s="36"/>
+      <c r="O4" s="36"/>
+      <c r="P4" s="40"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
@@ -2462,37 +2490,37 @@
       <c r="B8" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="25">
         <v>1331</v>
       </c>
-      <c r="D8" s="37">
+      <c r="D8" s="27">
         <v>1143.6600000000001</v>
       </c>
-      <c r="E8" s="37">
+      <c r="E8" s="27">
         <v>1110.93</v>
       </c>
-      <c r="F8" s="37">
+      <c r="F8" s="27">
         <v>32.729999999999997</v>
       </c>
-      <c r="G8" s="38">
+      <c r="G8" s="28">
         <v>1219.79</v>
       </c>
-      <c r="H8" s="37">
+      <c r="H8" s="27">
         <v>1172.05</v>
       </c>
-      <c r="I8" s="37">
+      <c r="I8" s="27">
         <v>47.74</v>
       </c>
-      <c r="J8" s="38">
+      <c r="J8" s="28">
         <v>1080.3499999999999</v>
       </c>
-      <c r="K8" s="37">
+      <c r="K8" s="27">
         <v>1061.71</v>
       </c>
-      <c r="L8" s="37">
+      <c r="L8" s="27">
         <v>18.64</v>
       </c>
-      <c r="M8" s="39">
+      <c r="M8" s="29">
         <v>0.88569130016964803</v>
       </c>
       <c r="N8" s="11">
@@ -2501,13 +2529,13 @@
       <c r="O8" s="11">
         <v>0.39627604911469866</v>
       </c>
-      <c r="P8" s="39">
+      <c r="P8" s="29">
         <v>0.94438776389571188</v>
       </c>
-      <c r="Q8" s="28">
+      <c r="Q8" s="26">
         <v>0.95520802465734078</v>
       </c>
-      <c r="R8" s="28">
+      <c r="R8" s="26">
         <v>0.54836554643792279</v>
       </c>
     </row>
@@ -2518,52 +2546,52 @@
       <c r="B9" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="27">
+      <c r="C9" s="25">
         <v>1000</v>
       </c>
-      <c r="D9" s="37">
+      <c r="D9" s="27">
         <v>860.01</v>
       </c>
-      <c r="E9" s="37">
+      <c r="E9" s="27">
         <v>835.4</v>
       </c>
-      <c r="F9" s="37">
+      <c r="F9" s="27">
         <v>24.61</v>
       </c>
-      <c r="G9" s="38">
+      <c r="G9" s="28">
         <v>916.12</v>
       </c>
-      <c r="H9" s="37">
+      <c r="H9" s="27">
         <v>878.68</v>
       </c>
-      <c r="I9" s="37">
+      <c r="I9" s="27">
         <v>37.44</v>
       </c>
-      <c r="J9" s="38">
+      <c r="J9" s="28">
         <v>811.97</v>
       </c>
-      <c r="K9" s="37">
+      <c r="K9" s="27">
         <v>797.8</v>
       </c>
-      <c r="L9" s="37">
+      <c r="L9" s="27">
         <v>14.17</v>
       </c>
-      <c r="M9" s="39">
+      <c r="M9" s="29">
         <v>0.88623349182234035</v>
       </c>
-      <c r="N9" s="28">
+      <c r="N9" s="26">
         <v>0.90855050698943884</v>
       </c>
-      <c r="O9" s="28">
+      <c r="O9" s="26">
         <v>0.3902462559028726</v>
       </c>
-      <c r="P9" s="39">
+      <c r="P9" s="29">
         <v>0.94383165349221299</v>
       </c>
-      <c r="Q9" s="28">
+      <c r="Q9" s="26">
         <v>0.95449551222090745</v>
       </c>
-      <c r="R9" s="28">
+      <c r="R9" s="26">
         <v>0.55833567435556519</v>
       </c>
     </row>
@@ -2680,24 +2708,24 @@
       </c>
     </row>
     <row r="15" spans="1:18" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="32" t="s">
+      <c r="A15" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="32"/>
-      <c r="C15" s="32"/>
-      <c r="D15" s="32"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="32"/>
-      <c r="G15" s="35"/>
-      <c r="H15" s="32"/>
-      <c r="I15" s="32"/>
-      <c r="J15" s="35"/>
-      <c r="K15" s="32"/>
-      <c r="L15" s="32"/>
-      <c r="M15" s="36"/>
-      <c r="N15" s="32"/>
-      <c r="O15" s="32"/>
-      <c r="P15" s="36"/>
+      <c r="B15" s="36"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="36"/>
+      <c r="F15" s="36"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="36"/>
+      <c r="I15" s="36"/>
+      <c r="J15" s="39"/>
+      <c r="K15" s="36"/>
+      <c r="L15" s="36"/>
+      <c r="M15" s="40"/>
+      <c r="N15" s="36"/>
+      <c r="O15" s="36"/>
+      <c r="P15" s="40"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
